--- a/assets/constructions/examples/ctd_mc2.xlsx
+++ b/assets/constructions/examples/ctd_mc2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,11 +669,36 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P3120717-16</t>
+          <t>P3120217-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -683,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P3120717</t>
+          <t>P3120217</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -704,29 +729,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HB-16</t>
+          <t>HB-12</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -749,7 +774,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PWZ-NORM XL</t>
+          <t>DIN 844 B</t>
         </is>
       </c>
       <c r="Z2" t="n">
@@ -759,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -807,68 +832,75 @@
       <c r="AV2" t="b">
         <v>1</v>
       </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6887 6.000</t>
+          <t>MC319-25.0W4BC-WK40TF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>MC319</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>MKS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>h10</t>
+          <t>h12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.12</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -884,13 +916,13 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>WK40TF</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>FIRE</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,35 +931,39 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>23.75</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>6</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
@@ -935,7 +971,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2019 - Guhring Фрезерный инструмент New Level</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -947,35 +983,42 @@
         <v>0</v>
       </c>
       <c r="AV3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6887 25.000</t>
+          <t>E5D73200B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>E5D73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>KN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>h10</t>
@@ -984,33 +1027,31 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>23.6</v>
+        <v>20</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1026,20 +1067,16 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>Micro Grain Carbide</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>FIRE</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>DIN 6527 L</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
@@ -1047,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -1060,7 +1097,7 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1077,7 +1114,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2019 - Guhring Фрезерный инструмент New Level</t>
+          <t>2020: www.yg1.co.kr/toolselection/main/</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -1090,71 +1127,74 @@
       </c>
       <c r="AV4" t="b">
         <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>KN</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>660W32009WW UNCOATED</t>
+          <t>R216.33-25040-AJ25U H10F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>660W</t>
+          <t>CoroMill® Plura R216.3x..40-AJ..U</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>22.42</v>
       </c>
       <c r="K5" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HB-32</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1162,7 +1202,9 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>15</v>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>h6</t>
@@ -1170,10 +1212,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>UNCOATED</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
+          <t>H10F</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1181,7 +1227,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>DIN 1835/8</t>
+          <t>COROMANT</t>
         </is>
       </c>
       <c r="Z5" t="n">
@@ -1191,44 +1237,54 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AC5" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>23.75</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.837</v>
+      </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t xml:space="preserve"> 01.1 </t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AU5" t="b">
@@ -1236,65 +1292,74 @@
       </c>
       <c r="AV5" t="b">
         <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3340 15.000</t>
+          <t>END MILL Ø16 FA505S V-MAXX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>VERGNANO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>FA505S</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>js12</t>
+          <t>k12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7</v>
+      </c>
       <c r="M6" t="n">
-        <v>26</v>
-      </c>
-      <c r="N6" t="n">
-        <v>26</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HB-12</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1308,20 +1373,16 @@
           <t>h6</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>HSS-E-PM</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>V-MAXX</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DIN 844 K</t>
+          <t>DIN 327</t>
         </is>
       </c>
       <c r="Z6" t="n">
@@ -1331,15 +1392,19 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>29</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1348,7 +1413,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr"/>
@@ -1361,12 +1426,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2019 - Guhring Фрезерный инструмент New Level</t>
+          <t>2022/Vergnano-End-Mills-Catalogue-65.pdf</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="AU6" t="b">
@@ -1374,6 +1439,17 @@
       </c>
       <c r="AV6" t="b">
         <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
   </sheetData>
